--- a/survey_templates/040_post_game_fan_feedback_poll--survey_templates.xlsx
+++ b/survey_templates/040_post_game_fan_feedback_poll--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'game_1'}</t>
+          <t>game_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Game 1'}</t>
+          <t>Game 1</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'game_2'}</t>
+          <t>game_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Game 2'}</t>
+          <t>Game 2</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'game_3'}</t>
+          <t>game_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Game 3'}</t>
+          <t>Game 3</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
